--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Real Madrid.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Real Madrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X20"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,73 +565,73 @@
         <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>69.7838</v>
+        <v>70.1225</v>
       </c>
       <c r="E2" t="n">
-        <v>55.4723</v>
+        <v>55.0922</v>
       </c>
       <c r="F2" t="n">
-        <v>14.311</v>
+        <v>15.0301</v>
       </c>
       <c r="G2" t="n">
-        <v>28.6382</v>
+        <v>28.8463</v>
       </c>
       <c r="H2" t="n">
-        <v>28.3427</v>
+        <v>28.3255</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2948000000000004</v>
+        <v>0.5208999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>37.9462</v>
+        <v>37.6336</v>
       </c>
       <c r="K2" t="n">
-        <v>32.0875</v>
+        <v>31.7874</v>
       </c>
       <c r="L2" t="n">
-        <v>5.858899999999999</v>
+        <v>5.846</v>
       </c>
       <c r="M2" t="n">
-        <v>-9.3085</v>
+        <v>-8.7872</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.7448</v>
+        <v>-3.462</v>
       </c>
       <c r="O2" t="n">
-        <v>-5.564</v>
+        <v>-5.3255</v>
       </c>
       <c r="P2" t="n">
-        <v>4.9906</v>
+        <v>5.0082</v>
       </c>
       <c r="Q2" t="n">
-        <v>-28.5809</v>
+        <v>-28.6815</v>
       </c>
       <c r="R2" t="n">
-        <v>33.5713</v>
+        <v>33.6897</v>
       </c>
       <c r="S2" t="n">
-        <v>31.2711</v>
+        <v>31.3806</v>
       </c>
       <c r="T2" t="n">
-        <v>24.2535</v>
+        <v>24.3925</v>
       </c>
       <c r="U2" t="n">
-        <v>7.0176</v>
+        <v>6.988099999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>4.8846</v>
+        <v>4.887700000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>21.8541</v>
+        <v>21.7478</v>
       </c>
       <c r="X2" t="n">
-        <v>-16.9693</v>
+        <v>-16.8601</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D3" t="n">
-        <v>31.7824</v>
+        <v>37.9006</v>
       </c>
       <c r="E3" t="n">
-        <v>14.3171</v>
+        <v>12.8548</v>
       </c>
       <c r="F3" t="n">
-        <v>17.4651</v>
+        <v>25.0462</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2773</v>
+        <v>4.019600000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.5763</v>
+        <v>11.5311</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8537</v>
+        <v>-7.511300000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>11.27</v>
+        <v>27.4939</v>
       </c>
       <c r="K3" t="n">
-        <v>4.416399999999999</v>
+        <v>22.2964</v>
       </c>
       <c r="L3" t="n">
-        <v>6.8538</v>
+        <v>5.1977</v>
       </c>
       <c r="M3" t="n">
-        <v>-8.992700000000001</v>
+        <v>-23.4746</v>
       </c>
       <c r="N3" t="n">
-        <v>-5.9924</v>
+        <v>-10.7659</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.9999</v>
+        <v>-12.7089</v>
       </c>
       <c r="P3" t="n">
-        <v>22.4566</v>
+        <v>-19.1208</v>
       </c>
       <c r="Q3" t="n">
-        <v>-8.392800000000001</v>
+        <v>-66.6961</v>
       </c>
       <c r="R3" t="n">
-        <v>30.8493</v>
+        <v>47.5752</v>
       </c>
       <c r="S3" t="n">
-        <v>13.0198</v>
+        <v>5.4576</v>
       </c>
       <c r="T3" t="n">
-        <v>6.7476</v>
+        <v>-3.378300000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>6.2719</v>
+        <v>8.836399999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>-5.9714</v>
+        <v>47.5443</v>
       </c>
       <c r="W3" t="n">
-        <v>4.6921</v>
+        <v>55.435</v>
       </c>
       <c r="X3" t="n">
-        <v>-10.6635</v>
+        <v>-7.8907</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>24.3713</v>
+        <v>27.176</v>
       </c>
       <c r="E4" t="n">
-        <v>9.840100000000001</v>
+        <v>17.2466</v>
       </c>
       <c r="F4" t="n">
-        <v>14.5315</v>
+        <v>9.9292</v>
       </c>
       <c r="G4" t="n">
-        <v>19.1186</v>
+        <v>0.8292999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>9.6394</v>
+        <v>0.7632999999999994</v>
       </c>
       <c r="I4" t="n">
-        <v>9.4793</v>
+        <v>0.06579999999999941</v>
       </c>
       <c r="J4" t="n">
-        <v>29.7489</v>
+        <v>17.8318</v>
       </c>
       <c r="K4" t="n">
-        <v>15.6225</v>
+        <v>10.1732</v>
       </c>
       <c r="L4" t="n">
-        <v>14.126</v>
+        <v>7.6588</v>
       </c>
       <c r="M4" t="n">
-        <v>-10.6304</v>
+        <v>-17.0029</v>
       </c>
       <c r="N4" t="n">
-        <v>-5.9832</v>
+        <v>-9.410299999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.6471</v>
+        <v>-7.5925</v>
       </c>
       <c r="P4" t="n">
-        <v>-25.6323</v>
+        <v>24.8121</v>
       </c>
       <c r="Q4" t="n">
-        <v>-57.8426</v>
+        <v>-12.2922</v>
       </c>
       <c r="R4" t="n">
-        <v>32.2104</v>
+        <v>37.1042</v>
       </c>
       <c r="S4" t="n">
-        <v>-8.779400000000001</v>
+        <v>12.0293</v>
       </c>
       <c r="T4" t="n">
-        <v>-8.0238</v>
+        <v>6.8759</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7557</v>
+        <v>5.1535</v>
       </c>
       <c r="V4" t="n">
-        <v>39.6641</v>
+        <v>-10.4941</v>
       </c>
       <c r="W4" t="n">
-        <v>45.9567</v>
+        <v>4.8313</v>
       </c>
       <c r="X4" t="n">
-        <v>-6.2929</v>
+        <v>-15.3254</v>
       </c>
     </row>
     <row r="5">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>21.9065</v>
+        <v>20.6521</v>
       </c>
       <c r="E5" t="n">
-        <v>21.3295</v>
+        <v>21.9907</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5772999999999997</v>
+        <v>-1.3388</v>
       </c>
       <c r="G5" t="n">
-        <v>16.1539</v>
+        <v>16.916</v>
       </c>
       <c r="H5" t="n">
-        <v>13.4316</v>
+        <v>14.7505</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7222</v>
+        <v>2.1652</v>
       </c>
       <c r="J5" t="n">
-        <v>18.9448</v>
+        <v>21.3947</v>
       </c>
       <c r="K5" t="n">
-        <v>14.8053</v>
+        <v>17.0458</v>
       </c>
       <c r="L5" t="n">
-        <v>4.1396</v>
+        <v>4.349</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.791</v>
+        <v>-4.4788</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3739</v>
+        <v>-2.2949</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4172</v>
+        <v>-2.1836</v>
       </c>
       <c r="P5" t="n">
-        <v>-7.258599999999999</v>
+        <v>-8.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>-23.3639</v>
+        <v>-26.8607</v>
       </c>
       <c r="R5" t="n">
-        <v>16.105</v>
+        <v>18.2105</v>
       </c>
       <c r="S5" t="n">
-        <v>16.9767</v>
+        <v>19.0023</v>
       </c>
       <c r="T5" t="n">
-        <v>14.3391</v>
+        <v>16.0438</v>
       </c>
       <c r="U5" t="n">
-        <v>2.6377</v>
+        <v>2.9584</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.9654</v>
+        <v>-6.615900000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>11.4095</v>
+        <v>11.4128</v>
       </c>
       <c r="X5" t="n">
-        <v>-15.3748</v>
+        <v>-18.0286</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
-        <v>21.6746</v>
+        <v>17.5757</v>
       </c>
       <c r="E6" t="n">
-        <v>3.612900000000001</v>
+        <v>5.4328</v>
       </c>
       <c r="F6" t="n">
-        <v>18.0622</v>
+        <v>12.143</v>
       </c>
       <c r="G6" t="n">
-        <v>-5.4877</v>
+        <v>21.3672</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9166</v>
+        <v>8.7592</v>
       </c>
       <c r="I6" t="n">
-        <v>-10.4045</v>
+        <v>12.6087</v>
       </c>
       <c r="J6" t="n">
-        <v>14.1496</v>
+        <v>36.1006</v>
       </c>
       <c r="K6" t="n">
-        <v>12.4922</v>
+        <v>18.5608</v>
       </c>
       <c r="L6" t="n">
-        <v>1.657499999999999</v>
+        <v>17.5394</v>
       </c>
       <c r="M6" t="n">
-        <v>-19.6371</v>
+        <v>-14.7328</v>
       </c>
       <c r="N6" t="n">
-        <v>-7.5755</v>
+        <v>-9.802</v>
       </c>
       <c r="O6" t="n">
-        <v>-12.0623</v>
+        <v>-4.931</v>
       </c>
       <c r="P6" t="n">
-        <v>-13.1561</v>
+        <v>-30.5027</v>
       </c>
       <c r="Q6" t="n">
-        <v>-53.0791</v>
+        <v>-70.3382</v>
       </c>
       <c r="R6" t="n">
-        <v>39.9225</v>
+        <v>39.8357</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2038</v>
+        <v>-12.3904</v>
       </c>
       <c r="T6" t="n">
-        <v>-4.0253</v>
+        <v>-11.1061</v>
       </c>
       <c r="U6" t="n">
-        <v>6.2291</v>
+        <v>-1.2842</v>
       </c>
       <c r="V6" t="n">
-        <v>38.115</v>
+        <v>39.1014</v>
       </c>
       <c r="W6" t="n">
-        <v>46.5674</v>
+        <v>50.7765</v>
       </c>
       <c r="X6" t="n">
-        <v>-8.452400000000001</v>
+        <v>-11.6753</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. PROCIDA</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>20.2197</v>
+        <v>16.8202</v>
       </c>
       <c r="E7" t="n">
-        <v>26.9644</v>
+        <v>22.5678</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.7447</v>
+        <v>-5.7478</v>
       </c>
       <c r="G7" t="n">
-        <v>26.9035</v>
+        <v>7.1201</v>
       </c>
       <c r="H7" t="n">
-        <v>15.6554</v>
+        <v>6.6563</v>
       </c>
       <c r="I7" t="n">
-        <v>11.2483</v>
+        <v>0.4639000000000002</v>
       </c>
       <c r="J7" t="n">
-        <v>33.3875</v>
+        <v>23.5635</v>
       </c>
       <c r="K7" t="n">
-        <v>21.2396</v>
+        <v>14.5968</v>
       </c>
       <c r="L7" t="n">
-        <v>12.148</v>
+        <v>8.9665</v>
       </c>
       <c r="M7" t="n">
-        <v>-6.4839</v>
+        <v>-16.4433</v>
       </c>
       <c r="N7" t="n">
-        <v>-5.584099999999999</v>
+        <v>-7.940799999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8995</v>
+        <v>-8.502600000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>5.8977</v>
+        <v>-2.9591</v>
       </c>
       <c r="Q7" t="n">
-        <v>-17.2394</v>
+        <v>-28.4542</v>
       </c>
       <c r="R7" t="n">
-        <v>23.1367</v>
+        <v>25.4948</v>
       </c>
       <c r="S7" t="n">
-        <v>-5.1127</v>
+        <v>19.847</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9497000000000002</v>
+        <v>15.9178</v>
       </c>
       <c r="U7" t="n">
-        <v>-6.0626</v>
+        <v>3.9296</v>
       </c>
       <c r="V7" t="n">
-        <v>-7.4687</v>
+        <v>-7.1881</v>
       </c>
       <c r="W7" t="n">
-        <v>9.8665</v>
+        <v>11.5406</v>
       </c>
       <c r="X7" t="n">
-        <v>-17.3351</v>
+        <v>-18.7287</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>18.4352</v>
+        <v>15.2228</v>
       </c>
       <c r="E8" t="n">
-        <v>18.7208</v>
+        <v>10.5559</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2853000000000002</v>
+        <v>4.6669</v>
       </c>
       <c r="G8" t="n">
-        <v>9.234299999999999</v>
+        <v>4.412100000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>6.9729</v>
+        <v>0.9964</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2613</v>
+        <v>3.416</v>
       </c>
       <c r="J8" t="n">
-        <v>21.1218</v>
+        <v>24.3521</v>
       </c>
       <c r="K8" t="n">
-        <v>13.0239</v>
+        <v>11.2554</v>
       </c>
       <c r="L8" t="n">
-        <v>8.0976</v>
+        <v>13.0963</v>
       </c>
       <c r="M8" t="n">
-        <v>-11.8876</v>
+        <v>-19.94</v>
       </c>
       <c r="N8" t="n">
-        <v>-6.0511</v>
+        <v>-10.2593</v>
       </c>
       <c r="O8" t="n">
-        <v>-5.8363</v>
+        <v>-9.6805</v>
       </c>
       <c r="P8" t="n">
-        <v>-4.0831</v>
+        <v>-12.2922</v>
       </c>
       <c r="Q8" t="n">
-        <v>-26.086</v>
+        <v>-44.6159</v>
       </c>
       <c r="R8" t="n">
-        <v>22.0027</v>
+        <v>32.3236</v>
       </c>
       <c r="S8" t="n">
-        <v>17.3271</v>
+        <v>7.6176</v>
       </c>
       <c r="T8" t="n">
-        <v>13.9789</v>
+        <v>-1.0489</v>
       </c>
       <c r="U8" t="n">
-        <v>3.3481</v>
+        <v>8.666700000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-4.0432</v>
+        <v>15.4853</v>
       </c>
       <c r="W8" t="n">
-        <v>9.7056</v>
+        <v>31.8686</v>
       </c>
       <c r="X8" t="n">
-        <v>-13.7489</v>
+        <v>-16.3829</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>I. ALMANSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>15.1984</v>
+        <v>14.2401</v>
       </c>
       <c r="E9" t="n">
-        <v>21.9608</v>
+        <v>26.2094</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.7627</v>
+        <v>-11.9693</v>
       </c>
       <c r="G9" t="n">
-        <v>9.5745</v>
+        <v>0.4062000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>11.5467</v>
+        <v>2.9274</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9721</v>
+        <v>-2.521</v>
       </c>
       <c r="J9" t="n">
-        <v>28.428</v>
+        <v>15.8051</v>
       </c>
       <c r="K9" t="n">
-        <v>21.5684</v>
+        <v>13.1316</v>
       </c>
       <c r="L9" t="n">
-        <v>6.8596</v>
+        <v>2.6731</v>
       </c>
       <c r="M9" t="n">
-        <v>-18.8534</v>
+        <v>-15.3987</v>
       </c>
       <c r="N9" t="n">
-        <v>-10.0214</v>
+        <v>-10.204</v>
       </c>
       <c r="O9" t="n">
-        <v>-8.8322</v>
+        <v>-5.1943</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6807000000000003</v>
+        <v>5.008</v>
       </c>
       <c r="Q9" t="n">
-        <v>-23.5907</v>
+        <v>-6.829000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>22.9102</v>
+        <v>11.8368</v>
       </c>
       <c r="S9" t="n">
-        <v>4.2281</v>
+        <v>10.2886</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5649</v>
+        <v>8.1157</v>
       </c>
       <c r="U9" t="n">
-        <v>1.6631</v>
+        <v>2.1728</v>
       </c>
       <c r="V9" t="n">
-        <v>2.076000000000001</v>
+        <v>-1.4627</v>
       </c>
       <c r="W9" t="n">
-        <v>14.5586</v>
+        <v>9.117599999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>-12.4825</v>
+        <v>-10.5804</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>G. PROCIDA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D10" t="n">
-        <v>13.8527</v>
+        <v>12.4772</v>
       </c>
       <c r="E10" t="n">
-        <v>10.9005</v>
+        <v>24.6413</v>
       </c>
       <c r="F10" t="n">
-        <v>2.952299999999999</v>
+        <v>-12.1643</v>
       </c>
       <c r="G10" t="n">
-        <v>6.595700000000002</v>
+        <v>20.4071</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3148</v>
+        <v>12.2264</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2806</v>
+        <v>8.1807</v>
       </c>
       <c r="J10" t="n">
-        <v>21.2438</v>
+        <v>32.7201</v>
       </c>
       <c r="K10" t="n">
-        <v>8.3283</v>
+        <v>21.5065</v>
       </c>
       <c r="L10" t="n">
-        <v>12.9153</v>
+        <v>11.2137</v>
       </c>
       <c r="M10" t="n">
-        <v>-14.6481</v>
+        <v>-12.3131</v>
       </c>
       <c r="N10" t="n">
-        <v>-6.0133</v>
+        <v>-9.280099999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-8.6349</v>
+        <v>-3.0326</v>
       </c>
       <c r="P10" t="n">
-        <v>-5.897699999999999</v>
+        <v>9.333</v>
       </c>
       <c r="Q10" t="n">
-        <v>-31.3031</v>
+        <v>-19.8041</v>
       </c>
       <c r="R10" t="n">
-        <v>25.4052</v>
+        <v>29.1368</v>
       </c>
       <c r="S10" t="n">
-        <v>4.811900000000001</v>
+        <v>-4.9806</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.8265</v>
+        <v>0.6577</v>
       </c>
       <c r="U10" t="n">
-        <v>6.638</v>
+        <v>-5.6381</v>
       </c>
       <c r="V10" t="n">
-        <v>8.3432</v>
+        <v>-12.2824</v>
       </c>
       <c r="W10" t="n">
-        <v>22.7862</v>
+        <v>11.0675</v>
       </c>
       <c r="X10" t="n">
-        <v>-14.443</v>
+        <v>-23.3498</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D11" t="n">
-        <v>12.7591</v>
+        <v>12.4558</v>
       </c>
       <c r="E11" t="n">
-        <v>11.7175</v>
+        <v>-1.5908</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0417</v>
+        <v>14.0469</v>
       </c>
       <c r="G11" t="n">
-        <v>39.0645</v>
+        <v>13.5254</v>
       </c>
       <c r="H11" t="n">
-        <v>17.5446</v>
+        <v>9.4757</v>
       </c>
       <c r="I11" t="n">
-        <v>21.5202</v>
+        <v>4.049799999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>54.8499</v>
+        <v>22.7408</v>
       </c>
       <c r="K11" t="n">
-        <v>23.9572</v>
+        <v>14.1336</v>
       </c>
       <c r="L11" t="n">
-        <v>30.8929</v>
+        <v>8.607399999999998</v>
       </c>
       <c r="M11" t="n">
-        <v>-15.7852</v>
+        <v>-9.2151</v>
       </c>
       <c r="N11" t="n">
-        <v>-6.4127</v>
+        <v>-4.6579</v>
       </c>
       <c r="O11" t="n">
-        <v>-9.3726</v>
+        <v>-4.5573</v>
       </c>
       <c r="P11" t="n">
-        <v>-13.6099</v>
+        <v>16.162</v>
       </c>
       <c r="Q11" t="n">
-        <v>-55.1203</v>
+        <v>-20.4869</v>
       </c>
       <c r="R11" t="n">
-        <v>41.5105</v>
+        <v>36.6491</v>
       </c>
       <c r="S11" t="n">
-        <v>-20.537</v>
+        <v>-19.8518</v>
       </c>
       <c r="T11" t="n">
-        <v>-15.9719</v>
+        <v>-13.6645</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.5651</v>
+        <v>-6.1875</v>
       </c>
       <c r="V11" t="n">
-        <v>7.840999999999999</v>
+        <v>2.6206</v>
       </c>
       <c r="W11" t="n">
-        <v>27.9596</v>
+        <v>9.82</v>
       </c>
       <c r="X11" t="n">
-        <v>-20.1185</v>
+        <v>-7.1995</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. ALMANSA</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D12" t="n">
-        <v>9.397600000000001</v>
+        <v>6.362299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>16.4635</v>
+        <v>10.681</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.066</v>
+        <v>-4.3184</v>
       </c>
       <c r="G12" t="n">
-        <v>3.7898</v>
+        <v>-0.3774000000000011</v>
       </c>
       <c r="H12" t="n">
-        <v>6.5483</v>
+        <v>1.899799999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.7586</v>
+        <v>-2.2776</v>
       </c>
       <c r="J12" t="n">
-        <v>12.1713</v>
+        <v>17.804</v>
       </c>
       <c r="K12" t="n">
-        <v>11.577</v>
+        <v>9.1069</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5942999999999999</v>
+        <v>8.6967</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.3813</v>
+        <v>-18.1816</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.0286</v>
+        <v>-7.2073</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.3531</v>
+        <v>-10.9745</v>
       </c>
       <c r="P12" t="n">
-        <v>2.0416</v>
+        <v>15.7067</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.7636</v>
+        <v>-15.4787</v>
       </c>
       <c r="R12" t="n">
-        <v>6.805</v>
+        <v>31.1858</v>
       </c>
       <c r="S12" t="n">
-        <v>4.4341</v>
+        <v>1.3721</v>
       </c>
       <c r="T12" t="n">
-        <v>3.6566</v>
+        <v>-0.3030000000000002</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7773</v>
+        <v>1.6753</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.8678000000000001</v>
+        <v>-10.3388</v>
       </c>
       <c r="W12" t="n">
-        <v>5.3992</v>
+        <v>8.6594</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.2671</v>
+        <v>-18.9981</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
-        <v>8.073399999999999</v>
+        <v>5.4334</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1629</v>
+        <v>4.704599999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9105</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5368000000000004</v>
+        <v>38.1412</v>
       </c>
       <c r="H13" t="n">
-        <v>4.0716</v>
+        <v>18.8466</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.6084</v>
+        <v>19.2948</v>
       </c>
       <c r="J13" t="n">
-        <v>8.598800000000001</v>
+        <v>58.477</v>
       </c>
       <c r="K13" t="n">
-        <v>8.610099999999999</v>
+        <v>27.9307</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.01120000000000054</v>
+        <v>30.5458</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.135400000000001</v>
+        <v>-20.3358</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.5385</v>
+        <v>-9.084299999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.5968</v>
+        <v>-11.2513</v>
       </c>
       <c r="P13" t="n">
-        <v>8.165900000000001</v>
+        <v>-17.0723</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.476</v>
+        <v>-64.8751</v>
       </c>
       <c r="R13" t="n">
-        <v>20.6419</v>
+        <v>47.803</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0213</v>
+        <v>-23.9123</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2664</v>
+        <v>-19.4173</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2877</v>
+        <v>-4.4948</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4656</v>
+        <v>8.276200000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>8.773899999999999</v>
+        <v>30.5201</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.3083</v>
+        <v>-22.2438</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14" t="n">
-        <v>4.590699999999999</v>
+        <v>1.325</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.354300000000002</v>
+        <v>13.2201</v>
       </c>
       <c r="F14" t="n">
-        <v>8.944800000000001</v>
+        <v>-11.8951</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.1651</v>
+        <v>3.0002</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1471</v>
+        <v>8.9839</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.3125</v>
+        <v>-5.9835</v>
       </c>
       <c r="J14" t="n">
-        <v>4.107600000000001</v>
+        <v>29.6574</v>
       </c>
       <c r="K14" t="n">
-        <v>8.7011</v>
+        <v>24.8553</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.593299999999999</v>
+        <v>4.802199999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.2729</v>
+        <v>-26.6576</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.553800000000001</v>
+        <v>-15.8716</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.7193</v>
+        <v>-10.7857</v>
       </c>
       <c r="P14" t="n">
-        <v>12.4759</v>
+        <v>-6.3738</v>
       </c>
       <c r="Q14" t="n">
-        <v>-19.0542</v>
+        <v>-34.6001</v>
       </c>
       <c r="R14" t="n">
-        <v>31.5298</v>
+        <v>28.2266</v>
       </c>
       <c r="S14" t="n">
-        <v>-15.9252</v>
+        <v>5.4127</v>
       </c>
       <c r="T14" t="n">
-        <v>-9.3332</v>
+        <v>2.1066</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.5923</v>
+        <v>3.3064</v>
       </c>
       <c r="V14" t="n">
-        <v>12.2058</v>
+        <v>-0.7138999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>19.9253</v>
+        <v>16.0565</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.7198</v>
+        <v>-16.7702</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>E. AMOSOV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.373499999999999</v>
+        <v>0.1292</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9919</v>
+        <v>-0.0352</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6183</v>
+        <v>0.1644</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.0483</v>
+        <v>0.3359</v>
       </c>
       <c r="H15" t="n">
-        <v>4.277700000000001</v>
+        <v>0.02</v>
       </c>
       <c r="I15" t="n">
-        <v>-5.326200000000001</v>
+        <v>0.3159</v>
       </c>
       <c r="J15" t="n">
-        <v>12.073</v>
+        <v>0.0345</v>
       </c>
       <c r="K15" t="n">
-        <v>8.0284</v>
+        <v>0.0345</v>
       </c>
       <c r="L15" t="n">
-        <v>4.044499999999999</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-13.1215</v>
+        <v>0.3014</v>
       </c>
       <c r="N15" t="n">
-        <v>-3.7506</v>
+        <v>-0.0144</v>
       </c>
       <c r="O15" t="n">
-        <v>-9.371</v>
+        <v>0.3159</v>
       </c>
       <c r="P15" t="n">
-        <v>11.7954</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-14.744</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>26.5396</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8857</v>
+        <v>-0.2067</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2069</v>
+        <v>-0.0697</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6789000000000001</v>
+        <v>-0.137</v>
       </c>
       <c r="V15" t="n">
-        <v>-8.2593</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>7.4561</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-15.7155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. AMOSOV</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1273</v>
+        <v>-0.05410000000000048</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0349</v>
+        <v>-6.6089</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1622</v>
+        <v>6.5549</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3333</v>
+        <v>-5.3431</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0187</v>
+        <v>2.3703</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3145</v>
+        <v>-7.7134</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0346</v>
+        <v>4.448700000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0346</v>
+        <v>9.5928</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-5.1441</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2986</v>
+        <v>-9.791600000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0159</v>
+        <v>-7.2227</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3145</v>
+        <v>-2.5693</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>7.284300000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-17.9831</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>25.2674</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.206</v>
+        <v>-1.6143</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0696</v>
+        <v>-1.4183</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1364</v>
+        <v>-0.1956000000000002</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.3808999999999996</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>8.3437</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-8.724600000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3389</v>
+        <v>-0.3439</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6952</v>
+        <v>-0.7016</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3563</v>
+        <v>0.3577</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4718</v>
+        <v>-0.4738</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6291</v>
+        <v>-0.6317</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1780,19 +1780,19 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0278</v>
+        <v>-0.0279</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0417</v>
+        <v>0.0418</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>O. YURTSEVEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6395000000000006</v>
+        <v>-2.539</v>
       </c>
       <c r="E18" t="n">
-        <v>-11.1237</v>
+        <v>-3.1747</v>
       </c>
       <c r="F18" t="n">
-        <v>10.4841</v>
+        <v>0.6355999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6013000000000002</v>
+        <v>1.0005</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3645</v>
+        <v>1.0058</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.9663</v>
+        <v>-0.005200000000000093</v>
       </c>
       <c r="J18" t="n">
-        <v>9.7338</v>
+        <v>3.1904</v>
       </c>
       <c r="K18" t="n">
-        <v>8.0457</v>
+        <v>2.3712</v>
       </c>
       <c r="L18" t="n">
-        <v>1.6885</v>
+        <v>0.8192</v>
       </c>
       <c r="M18" t="n">
-        <v>-10.3353</v>
+        <v>-2.1899</v>
       </c>
       <c r="N18" t="n">
-        <v>-3.6812</v>
+        <v>-1.3654</v>
       </c>
       <c r="O18" t="n">
-        <v>-6.6547</v>
+        <v>-0.8244999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>13.1563</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q18" t="n">
-        <v>-16.7856</v>
+        <v>-5.9184</v>
       </c>
       <c r="R18" t="n">
-        <v>29.942</v>
+        <v>2.9593</v>
       </c>
       <c r="S18" t="n">
-        <v>-15.5917</v>
+        <v>-0.4226</v>
       </c>
       <c r="T18" t="n">
-        <v>-11.5925</v>
+        <v>-0.6044</v>
       </c>
       <c r="U18" t="n">
-        <v>-3.9993</v>
+        <v>0.1818</v>
       </c>
       <c r="V18" t="n">
-        <v>2.3974</v>
+        <v>-0.1577999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>7.5203</v>
+        <v>0.1578</v>
       </c>
       <c r="X18" t="n">
-        <v>-5.1229</v>
+        <v>-0.3155999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1891,145 +1891,223 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4029</v>
+        <v>-3.3902</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3835</v>
+        <v>-0.4225</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.0194</v>
+        <v>-2.9677</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.5449</v>
+        <v>-3.5417</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.3534</v>
+        <v>-2.3578</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1915</v>
+        <v>-1.1839</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4351999999999999</v>
+        <v>0.4011</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5723</v>
+        <v>-0.6043000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0076</v>
+        <v>1.0054</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.98</v>
+        <v>-3.9427</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7811</v>
+        <v>-1.7535</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.199</v>
+        <v>-2.1893</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.5367</v>
+        <v>-4.552700000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S19" t="n">
-        <v>3.208</v>
+        <v>3.2213</v>
       </c>
       <c r="T19" t="n">
-        <v>3.3965</v>
+        <v>3.4135</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1885</v>
+        <v>-0.1922</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3214</v>
+        <v>0.3156</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>S. LLULL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>33</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-8.4095</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-12.1328</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.7231</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-17.5203</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-2.8449</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-14.6758</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.887900000000001</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6.6554</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-4.7679</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-19.4087</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-9.908100000000001</v>
+      </c>
+      <c r="P20" t="n">
+        <v>15.9343</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-23.2188</v>
+      </c>
+      <c r="R20" t="n">
+        <v>39.1529</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-21.9727</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-14.9429</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-7.029500000000001</v>
+      </c>
+      <c r="V20" t="n">
+        <v>15.1496</v>
+      </c>
+      <c r="W20" t="n">
+        <v>24.1409</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-8.991399999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Real Madrid</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>27</v>
-      </c>
-      <c r="D20" t="n">
-        <v>272.1649</v>
-      </c>
-      <c r="E20" t="n">
-        <v>205.8626</v>
-      </c>
-      <c r="F20" t="n">
-        <v>66.3026</v>
-      </c>
-      <c r="G20" t="n">
-        <v>145.8277</v>
-      </c>
-      <c r="H20" t="n">
-        <v>130.0202</v>
-      </c>
-      <c r="I20" t="n">
-        <v>15.8057</v>
-      </c>
-      <c r="J20" t="n">
-        <v>317.4584</v>
-      </c>
-      <c r="K20" t="n">
-        <v>211.9659</v>
-      </c>
-      <c r="L20" t="n">
-        <v>105.4932</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-171.6312</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-81.9448</v>
-      </c>
-      <c r="O20" t="n">
-        <v>-89.68810000000001</v>
-      </c>
-      <c r="P20" t="n">
-        <v>9.073800000000006</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>-396.9589</v>
-      </c>
-      <c r="R20" t="n">
-        <v>406.0309</v>
-      </c>
-      <c r="S20" t="n">
-        <v>32.1652</v>
-      </c>
-      <c r="T20" t="n">
-        <v>20.4477</v>
-      </c>
-      <c r="U20" t="n">
-        <v>11.7158</v>
-      </c>
-      <c r="V20" t="n">
-        <v>85.09929999999999</v>
-      </c>
-      <c r="W20" t="n">
-        <v>264.9132</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-179.8142</v>
+      <c r="C21" t="n">
+        <v>33</v>
+      </c>
+      <c r="D21" t="n">
+        <v>243.1562</v>
+      </c>
+      <c r="E21" t="n">
+        <v>200.5307</v>
+      </c>
+      <c r="F21" t="n">
+        <v>42.62489999999999</v>
+      </c>
+      <c r="G21" t="n">
+        <v>133.0708</v>
+      </c>
+      <c r="H21" t="n">
+        <v>124.4934</v>
+      </c>
+      <c r="I21" t="n">
+        <v>8.578299999999999</v>
+      </c>
+      <c r="J21" t="n">
+        <v>374.7476</v>
+      </c>
+      <c r="K21" t="n">
+        <v>254.4299999999999</v>
+      </c>
+      <c r="L21" t="n">
+        <v>120.3156</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-241.6771</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-129.9385</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-111.7377</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-2.274899999999999</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-491.6857</v>
+      </c>
+      <c r="R21" t="n">
+        <v>489.4105999999999</v>
+      </c>
+      <c r="S21" t="n">
+        <v>30.2498</v>
+      </c>
+      <c r="T21" t="n">
+        <v>11.5004</v>
+      </c>
+      <c r="U21" t="n">
+        <v>18.7519</v>
+      </c>
+      <c r="V21" t="n">
+        <v>82.11190000000002</v>
+      </c>
+      <c r="W21" t="n">
+        <v>305.9695</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-223.8571</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Real Madrid.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Real Madrid.xlsx
@@ -565,13 +565,13 @@
         <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>70.1225</v>
+        <v>49.4698</v>
       </c>
       <c r="E2" t="n">
-        <v>55.0922</v>
+        <v>37.2212</v>
       </c>
       <c r="F2" t="n">
-        <v>15.0301</v>
+        <v>12.2487</v>
       </c>
       <c r="G2" t="n">
         <v>28.8463</v>
@@ -610,13 +610,13 @@
         <v>33.6897</v>
       </c>
       <c r="S2" t="n">
-        <v>31.3806</v>
+        <v>10.7279</v>
       </c>
       <c r="T2" t="n">
-        <v>24.3925</v>
+        <v>6.521100000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>6.988099999999999</v>
+        <v>4.2066</v>
       </c>
       <c r="V2" t="n">
         <v>4.887700000000001</v>
@@ -643,13 +643,13 @@
         <v>28</v>
       </c>
       <c r="D3" t="n">
-        <v>37.9006</v>
+        <v>39.9544</v>
       </c>
       <c r="E3" t="n">
-        <v>12.8548</v>
+        <v>18.0946</v>
       </c>
       <c r="F3" t="n">
-        <v>25.0462</v>
+        <v>21.8598</v>
       </c>
       <c r="G3" t="n">
         <v>4.019600000000001</v>
@@ -688,13 +688,13 @@
         <v>47.5752</v>
       </c>
       <c r="S3" t="n">
-        <v>5.4576</v>
+        <v>7.5114</v>
       </c>
       <c r="T3" t="n">
-        <v>-3.378300000000001</v>
+        <v>1.8615</v>
       </c>
       <c r="U3" t="n">
-        <v>8.836399999999999</v>
+        <v>5.649999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>47.5443</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>27.176</v>
+        <v>30.3865</v>
       </c>
       <c r="E4" t="n">
-        <v>17.2466</v>
+        <v>14.6582</v>
       </c>
       <c r="F4" t="n">
-        <v>9.9292</v>
+        <v>15.7288</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8292999999999999</v>
+        <v>21.3672</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7632999999999994</v>
+        <v>8.7592</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06579999999999941</v>
+        <v>12.6087</v>
       </c>
       <c r="J4" t="n">
-        <v>17.8318</v>
+        <v>36.1006</v>
       </c>
       <c r="K4" t="n">
-        <v>10.1732</v>
+        <v>18.5608</v>
       </c>
       <c r="L4" t="n">
-        <v>7.6588</v>
+        <v>17.5394</v>
       </c>
       <c r="M4" t="n">
-        <v>-17.0029</v>
+        <v>-14.7328</v>
       </c>
       <c r="N4" t="n">
-        <v>-9.410299999999999</v>
+        <v>-9.802</v>
       </c>
       <c r="O4" t="n">
-        <v>-7.5925</v>
+        <v>-4.931</v>
       </c>
       <c r="P4" t="n">
-        <v>24.8121</v>
+        <v>-30.5027</v>
       </c>
       <c r="Q4" t="n">
-        <v>-12.2922</v>
+        <v>-70.3382</v>
       </c>
       <c r="R4" t="n">
-        <v>37.1042</v>
+        <v>39.8357</v>
       </c>
       <c r="S4" t="n">
-        <v>12.0293</v>
+        <v>0.4204</v>
       </c>
       <c r="T4" t="n">
-        <v>6.8759</v>
+        <v>-1.881</v>
       </c>
       <c r="U4" t="n">
-        <v>5.1535</v>
+        <v>2.3014</v>
       </c>
       <c r="V4" t="n">
-        <v>-10.4941</v>
+        <v>39.1014</v>
       </c>
       <c r="W4" t="n">
-        <v>4.8313</v>
+        <v>50.7765</v>
       </c>
       <c r="X4" t="n">
-        <v>-15.3254</v>
+        <v>-11.6753</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>20.6521</v>
+        <v>26.5389</v>
       </c>
       <c r="E5" t="n">
-        <v>21.9907</v>
+        <v>15.8812</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3388</v>
+        <v>10.6573</v>
       </c>
       <c r="G5" t="n">
-        <v>16.916</v>
+        <v>0.8292999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>14.7505</v>
+        <v>0.7632999999999994</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1652</v>
+        <v>0.06579999999999941</v>
       </c>
       <c r="J5" t="n">
-        <v>21.3947</v>
+        <v>17.8318</v>
       </c>
       <c r="K5" t="n">
-        <v>17.0458</v>
+        <v>10.1732</v>
       </c>
       <c r="L5" t="n">
-        <v>4.349</v>
+        <v>7.6588</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.4788</v>
+        <v>-17.0029</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.2949</v>
+        <v>-9.410299999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.1836</v>
+        <v>-7.5925</v>
       </c>
       <c r="P5" t="n">
-        <v>-8.65</v>
+        <v>24.8121</v>
       </c>
       <c r="Q5" t="n">
-        <v>-26.8607</v>
+        <v>-12.2922</v>
       </c>
       <c r="R5" t="n">
-        <v>18.2105</v>
+        <v>37.1042</v>
       </c>
       <c r="S5" t="n">
-        <v>19.0023</v>
+        <v>11.3922</v>
       </c>
       <c r="T5" t="n">
-        <v>16.0438</v>
+        <v>5.5103</v>
       </c>
       <c r="U5" t="n">
-        <v>2.9584</v>
+        <v>5.8814</v>
       </c>
       <c r="V5" t="n">
-        <v>-6.615900000000001</v>
+        <v>-10.4941</v>
       </c>
       <c r="W5" t="n">
-        <v>11.4128</v>
+        <v>4.8313</v>
       </c>
       <c r="X5" t="n">
-        <v>-18.0286</v>
+        <v>-15.3254</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>28</v>
       </c>
       <c r="D6" t="n">
-        <v>17.5757</v>
+        <v>26.3063</v>
       </c>
       <c r="E6" t="n">
-        <v>5.4328</v>
+        <v>19.1347</v>
       </c>
       <c r="F6" t="n">
-        <v>12.143</v>
+        <v>7.171800000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>21.3672</v>
+        <v>38.1412</v>
       </c>
       <c r="H6" t="n">
-        <v>8.7592</v>
+        <v>18.8466</v>
       </c>
       <c r="I6" t="n">
-        <v>12.6087</v>
+        <v>19.2948</v>
       </c>
       <c r="J6" t="n">
-        <v>36.1006</v>
+        <v>58.477</v>
       </c>
       <c r="K6" t="n">
-        <v>18.5608</v>
+        <v>27.9307</v>
       </c>
       <c r="L6" t="n">
-        <v>17.5394</v>
+        <v>30.5458</v>
       </c>
       <c r="M6" t="n">
-        <v>-14.7328</v>
+        <v>-20.3358</v>
       </c>
       <c r="N6" t="n">
-        <v>-9.802</v>
+        <v>-9.084299999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.931</v>
+        <v>-11.2513</v>
       </c>
       <c r="P6" t="n">
-        <v>-30.5027</v>
+        <v>-17.0723</v>
       </c>
       <c r="Q6" t="n">
-        <v>-70.3382</v>
+        <v>-64.8751</v>
       </c>
       <c r="R6" t="n">
-        <v>39.8357</v>
+        <v>47.803</v>
       </c>
       <c r="S6" t="n">
-        <v>-12.3904</v>
+        <v>-3.039</v>
       </c>
       <c r="T6" t="n">
-        <v>-11.1061</v>
+        <v>-4.9875</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2842</v>
+        <v>1.9484</v>
       </c>
       <c r="V6" t="n">
-        <v>39.1014</v>
+        <v>8.276200000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>50.7765</v>
+        <v>30.5201</v>
       </c>
       <c r="X6" t="n">
-        <v>-11.6753</v>
+        <v>-22.2438</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D7" t="n">
-        <v>16.8202</v>
+        <v>25.4624</v>
       </c>
       <c r="E7" t="n">
-        <v>22.5678</v>
+        <v>7.0492</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.7478</v>
+        <v>18.4132</v>
       </c>
       <c r="G7" t="n">
-        <v>7.1201</v>
+        <v>13.5254</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6563</v>
+        <v>9.4757</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4639000000000002</v>
+        <v>4.049799999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>23.5635</v>
+        <v>22.7408</v>
       </c>
       <c r="K7" t="n">
-        <v>14.5968</v>
+        <v>14.1336</v>
       </c>
       <c r="L7" t="n">
-        <v>8.9665</v>
+        <v>8.607399999999998</v>
       </c>
       <c r="M7" t="n">
-        <v>-16.4433</v>
+        <v>-9.2151</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.940799999999999</v>
+        <v>-4.6579</v>
       </c>
       <c r="O7" t="n">
-        <v>-8.502600000000001</v>
+        <v>-4.5573</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.9591</v>
+        <v>16.162</v>
       </c>
       <c r="Q7" t="n">
-        <v>-28.4542</v>
+        <v>-20.4869</v>
       </c>
       <c r="R7" t="n">
-        <v>25.4948</v>
+        <v>36.6491</v>
       </c>
       <c r="S7" t="n">
-        <v>19.847</v>
+        <v>-6.8459</v>
       </c>
       <c r="T7" t="n">
-        <v>15.9178</v>
+        <v>-5.0252</v>
       </c>
       <c r="U7" t="n">
-        <v>3.9296</v>
+        <v>-1.8212</v>
       </c>
       <c r="V7" t="n">
-        <v>-7.1881</v>
+        <v>2.6206</v>
       </c>
       <c r="W7" t="n">
-        <v>11.5406</v>
+        <v>9.82</v>
       </c>
       <c r="X7" t="n">
-        <v>-18.7287</v>
+        <v>-7.1995</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>G. PROCIDA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>15.2228</v>
+        <v>16.9031</v>
       </c>
       <c r="E8" t="n">
-        <v>10.5559</v>
+        <v>24.7945</v>
       </c>
       <c r="F8" t="n">
-        <v>4.6669</v>
+        <v>-7.8916</v>
       </c>
       <c r="G8" t="n">
-        <v>4.412100000000001</v>
+        <v>20.4071</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9964</v>
+        <v>12.2264</v>
       </c>
       <c r="I8" t="n">
-        <v>3.416</v>
+        <v>8.1807</v>
       </c>
       <c r="J8" t="n">
-        <v>24.3521</v>
+        <v>32.7201</v>
       </c>
       <c r="K8" t="n">
-        <v>11.2554</v>
+        <v>21.5065</v>
       </c>
       <c r="L8" t="n">
-        <v>13.0963</v>
+        <v>11.2137</v>
       </c>
       <c r="M8" t="n">
-        <v>-19.94</v>
+        <v>-12.3131</v>
       </c>
       <c r="N8" t="n">
-        <v>-10.2593</v>
+        <v>-9.280099999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-9.6805</v>
+        <v>-3.0326</v>
       </c>
       <c r="P8" t="n">
-        <v>-12.2922</v>
+        <v>9.333</v>
       </c>
       <c r="Q8" t="n">
-        <v>-44.6159</v>
+        <v>-19.8041</v>
       </c>
       <c r="R8" t="n">
-        <v>32.3236</v>
+        <v>29.1368</v>
       </c>
       <c r="S8" t="n">
-        <v>7.6176</v>
+        <v>-0.5545000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0489</v>
+        <v>0.8109999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>8.666700000000001</v>
+        <v>-1.3653</v>
       </c>
       <c r="V8" t="n">
-        <v>15.4853</v>
+        <v>-12.2824</v>
       </c>
       <c r="W8" t="n">
-        <v>31.8686</v>
+        <v>11.0675</v>
       </c>
       <c r="X8" t="n">
-        <v>-16.3829</v>
+        <v>-23.3498</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. ALMANSA</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>14.2401</v>
+        <v>13.3372</v>
       </c>
       <c r="E9" t="n">
-        <v>26.2094</v>
+        <v>12.2008</v>
       </c>
       <c r="F9" t="n">
-        <v>-11.9693</v>
+        <v>1.137099999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4062000000000001</v>
+        <v>4.412100000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9274</v>
+        <v>0.9964</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.521</v>
+        <v>3.416</v>
       </c>
       <c r="J9" t="n">
-        <v>15.8051</v>
+        <v>24.3521</v>
       </c>
       <c r="K9" t="n">
-        <v>13.1316</v>
+        <v>11.2554</v>
       </c>
       <c r="L9" t="n">
-        <v>2.6731</v>
+        <v>13.0963</v>
       </c>
       <c r="M9" t="n">
-        <v>-15.3987</v>
+        <v>-19.94</v>
       </c>
       <c r="N9" t="n">
-        <v>-10.204</v>
+        <v>-10.2593</v>
       </c>
       <c r="O9" t="n">
-        <v>-5.1943</v>
+        <v>-9.6805</v>
       </c>
       <c r="P9" t="n">
-        <v>5.008</v>
+        <v>-12.2922</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.829000000000001</v>
+        <v>-44.6159</v>
       </c>
       <c r="R9" t="n">
-        <v>11.8368</v>
+        <v>32.3236</v>
       </c>
       <c r="S9" t="n">
-        <v>10.2886</v>
+        <v>5.7319</v>
       </c>
       <c r="T9" t="n">
-        <v>8.1157</v>
+        <v>0.5959000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1728</v>
+        <v>5.1365</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4627</v>
+        <v>15.4853</v>
       </c>
       <c r="W9" t="n">
-        <v>9.117599999999999</v>
+        <v>31.8686</v>
       </c>
       <c r="X9" t="n">
-        <v>-10.5804</v>
+        <v>-16.3829</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. PROCIDA</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D10" t="n">
-        <v>12.4772</v>
+        <v>10.832</v>
       </c>
       <c r="E10" t="n">
-        <v>24.6413</v>
+        <v>1.328599999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-12.1643</v>
+        <v>9.5031</v>
       </c>
       <c r="G10" t="n">
-        <v>20.4071</v>
+        <v>-17.5203</v>
       </c>
       <c r="H10" t="n">
-        <v>12.2264</v>
+        <v>-2.8449</v>
       </c>
       <c r="I10" t="n">
-        <v>8.1807</v>
+        <v>-14.6758</v>
       </c>
       <c r="J10" t="n">
-        <v>32.7201</v>
+        <v>1.887900000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>21.5065</v>
+        <v>6.6554</v>
       </c>
       <c r="L10" t="n">
-        <v>11.2137</v>
+        <v>-4.7679</v>
       </c>
       <c r="M10" t="n">
-        <v>-12.3131</v>
+        <v>-19.4087</v>
       </c>
       <c r="N10" t="n">
-        <v>-9.280099999999999</v>
+        <v>-9.5</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.0326</v>
+        <v>-9.908100000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>9.333</v>
+        <v>15.9343</v>
       </c>
       <c r="Q10" t="n">
-        <v>-19.8041</v>
+        <v>-23.2188</v>
       </c>
       <c r="R10" t="n">
-        <v>29.1368</v>
+        <v>39.1529</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.9806</v>
+        <v>-2.7312</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6577</v>
+        <v>-1.4819</v>
       </c>
       <c r="U10" t="n">
-        <v>-5.6381</v>
+        <v>-1.2494</v>
       </c>
       <c r="V10" t="n">
-        <v>-12.2824</v>
+        <v>15.1496</v>
       </c>
       <c r="W10" t="n">
-        <v>11.0675</v>
+        <v>24.1409</v>
       </c>
       <c r="X10" t="n">
-        <v>-23.3498</v>
+        <v>-8.991399999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D11" t="n">
-        <v>12.4558</v>
+        <v>10.15</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5908</v>
+        <v>12.6112</v>
       </c>
       <c r="F11" t="n">
-        <v>14.0469</v>
+        <v>-2.4612</v>
       </c>
       <c r="G11" t="n">
-        <v>13.5254</v>
+        <v>-0.3774000000000011</v>
       </c>
       <c r="H11" t="n">
-        <v>9.4757</v>
+        <v>1.899799999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>4.049799999999999</v>
+        <v>-2.2776</v>
       </c>
       <c r="J11" t="n">
-        <v>22.7408</v>
+        <v>17.804</v>
       </c>
       <c r="K11" t="n">
-        <v>14.1336</v>
+        <v>9.1069</v>
       </c>
       <c r="L11" t="n">
-        <v>8.607399999999998</v>
+        <v>8.6967</v>
       </c>
       <c r="M11" t="n">
-        <v>-9.2151</v>
+        <v>-18.1816</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.6579</v>
+        <v>-7.2073</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.5573</v>
+        <v>-10.9745</v>
       </c>
       <c r="P11" t="n">
-        <v>16.162</v>
+        <v>15.7067</v>
       </c>
       <c r="Q11" t="n">
-        <v>-20.4869</v>
+        <v>-15.4787</v>
       </c>
       <c r="R11" t="n">
-        <v>36.6491</v>
+        <v>31.1858</v>
       </c>
       <c r="S11" t="n">
-        <v>-19.8518</v>
+        <v>5.1596</v>
       </c>
       <c r="T11" t="n">
-        <v>-13.6645</v>
+        <v>1.6271</v>
       </c>
       <c r="U11" t="n">
-        <v>-6.1875</v>
+        <v>3.5326</v>
       </c>
       <c r="V11" t="n">
-        <v>2.6206</v>
+        <v>-10.3388</v>
       </c>
       <c r="W11" t="n">
-        <v>9.82</v>
+        <v>8.6594</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.1995</v>
+        <v>-18.9981</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>6.362299999999999</v>
+        <v>10.0207</v>
       </c>
       <c r="E12" t="n">
-        <v>10.681</v>
+        <v>12.0132</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.3184</v>
+        <v>-1.993</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3774000000000011</v>
+        <v>16.916</v>
       </c>
       <c r="H12" t="n">
-        <v>1.899799999999999</v>
+        <v>14.7505</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.2776</v>
+        <v>2.1652</v>
       </c>
       <c r="J12" t="n">
-        <v>17.804</v>
+        <v>21.3947</v>
       </c>
       <c r="K12" t="n">
-        <v>9.1069</v>
+        <v>17.0458</v>
       </c>
       <c r="L12" t="n">
-        <v>8.6967</v>
+        <v>4.349</v>
       </c>
       <c r="M12" t="n">
-        <v>-18.1816</v>
+        <v>-4.4788</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.2073</v>
+        <v>-2.2949</v>
       </c>
       <c r="O12" t="n">
-        <v>-10.9745</v>
+        <v>-2.1836</v>
       </c>
       <c r="P12" t="n">
-        <v>15.7067</v>
+        <v>-8.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>-15.4787</v>
+        <v>-26.8607</v>
       </c>
       <c r="R12" t="n">
-        <v>31.1858</v>
+        <v>18.2105</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3721</v>
+        <v>8.3704</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3030000000000002</v>
+        <v>6.0666</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6753</v>
+        <v>2.304</v>
       </c>
       <c r="V12" t="n">
-        <v>-10.3388</v>
+        <v>-6.615900000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>8.6594</v>
+        <v>11.4128</v>
       </c>
       <c r="X12" t="n">
-        <v>-18.9981</v>
+        <v>-18.0286</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>I. ALMANSA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4334</v>
+        <v>8.852200000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>4.704599999999998</v>
+        <v>20.4408</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7282999999999999</v>
+        <v>-11.5884</v>
       </c>
       <c r="G13" t="n">
-        <v>38.1412</v>
+        <v>0.4062000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>18.8466</v>
+        <v>2.9274</v>
       </c>
       <c r="I13" t="n">
-        <v>19.2948</v>
+        <v>-2.521</v>
       </c>
       <c r="J13" t="n">
-        <v>58.477</v>
+        <v>15.8051</v>
       </c>
       <c r="K13" t="n">
-        <v>27.9307</v>
+        <v>13.1316</v>
       </c>
       <c r="L13" t="n">
-        <v>30.5458</v>
+        <v>2.6731</v>
       </c>
       <c r="M13" t="n">
-        <v>-20.3358</v>
+        <v>-15.3987</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.084299999999999</v>
+        <v>-10.204</v>
       </c>
       <c r="O13" t="n">
-        <v>-11.2513</v>
+        <v>-5.1943</v>
       </c>
       <c r="P13" t="n">
-        <v>-17.0723</v>
+        <v>5.008</v>
       </c>
       <c r="Q13" t="n">
-        <v>-64.8751</v>
+        <v>-6.829000000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>47.803</v>
+        <v>11.8368</v>
       </c>
       <c r="S13" t="n">
-        <v>-23.9123</v>
+        <v>4.9006</v>
       </c>
       <c r="T13" t="n">
-        <v>-19.4173</v>
+        <v>2.3469</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.4948</v>
+        <v>2.5538</v>
       </c>
       <c r="V13" t="n">
-        <v>8.276200000000001</v>
+        <v>-1.4627</v>
       </c>
       <c r="W13" t="n">
-        <v>30.5201</v>
+        <v>9.117599999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-22.2438</v>
+        <v>-10.5804</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>1.325</v>
+        <v>5.5381</v>
       </c>
       <c r="E14" t="n">
-        <v>13.2201</v>
+        <v>11.9705</v>
       </c>
       <c r="F14" t="n">
-        <v>-11.8951</v>
+        <v>-6.4323</v>
       </c>
       <c r="G14" t="n">
-        <v>3.0002</v>
+        <v>7.1201</v>
       </c>
       <c r="H14" t="n">
-        <v>8.9839</v>
+        <v>6.6563</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.9835</v>
+        <v>0.4639000000000002</v>
       </c>
       <c r="J14" t="n">
-        <v>29.6574</v>
+        <v>23.5635</v>
       </c>
       <c r="K14" t="n">
-        <v>24.8553</v>
+        <v>14.5968</v>
       </c>
       <c r="L14" t="n">
-        <v>4.802199999999999</v>
+        <v>8.9665</v>
       </c>
       <c r="M14" t="n">
-        <v>-26.6576</v>
+        <v>-16.4433</v>
       </c>
       <c r="N14" t="n">
-        <v>-15.8716</v>
+        <v>-7.940799999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-10.7857</v>
+        <v>-8.502600000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-6.3738</v>
+        <v>-2.9591</v>
       </c>
       <c r="Q14" t="n">
-        <v>-34.6001</v>
+        <v>-28.4542</v>
       </c>
       <c r="R14" t="n">
-        <v>28.2266</v>
+        <v>25.4948</v>
       </c>
       <c r="S14" t="n">
-        <v>5.4127</v>
+        <v>8.5655</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1066</v>
+        <v>5.3206</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3064</v>
+        <v>3.2449</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7138999999999999</v>
+        <v>-7.1881</v>
       </c>
       <c r="W14" t="n">
-        <v>16.0565</v>
+        <v>11.5406</v>
       </c>
       <c r="X14" t="n">
-        <v>-16.7702</v>
+        <v>-18.7287</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. AMOSOV</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1292</v>
+        <v>3.8869</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0352</v>
+        <v>14.7045</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1644</v>
+        <v>-10.8175</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3359</v>
+        <v>3.0002</v>
       </c>
       <c r="H15" t="n">
-        <v>0.02</v>
+        <v>8.9839</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3159</v>
+        <v>-5.9835</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0345</v>
+        <v>29.6574</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0345</v>
+        <v>24.8553</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4.802199999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3014</v>
+        <v>-26.6576</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0144</v>
+        <v>-15.8716</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3159</v>
+        <v>-10.7857</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-6.3738</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-34.6001</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>28.2266</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2067</v>
+        <v>7.9743</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0697</v>
+        <v>3.5905</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.137</v>
+        <v>4.384</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.7138999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>16.0565</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-16.7702</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>17</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.05410000000000048</v>
+        <v>2.523200000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.6089</v>
+        <v>-5.765700000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>6.5549</v>
+        <v>8.2889</v>
       </c>
       <c r="G16" t="n">
         <v>-5.3431</v>
@@ -1702,13 +1702,13 @@
         <v>25.2674</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6143</v>
+        <v>0.9632000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4183</v>
+        <v>-0.5749</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1956000000000002</v>
+        <v>1.5382</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3808999999999996</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. GRINVALDS</t>
+          <t>E. AMOSOV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3439</v>
+        <v>0.1605</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7016</v>
+        <v>-0.0352</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3577</v>
+        <v>0.1958</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4738</v>
+        <v>0.3359</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1579</v>
+        <v>0.02</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6317</v>
+        <v>0.3159</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7896</v>
+        <v>0.0345</v>
       </c>
       <c r="K17" t="n">
+        <v>0.0345</v>
+      </c>
+      <c r="L17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
-        <v>-0.7896</v>
-      </c>
       <c r="M17" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.0144</v>
+      </c>
+      <c r="O17" t="n">
         <v>0.3159</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.1579</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.1579</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1780,19 +1780,19 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0279</v>
+        <v>-0.1754</v>
       </c>
       <c r="T17" t="n">
         <v>-0.0697</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0418</v>
+        <v>-0.1057</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1578</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1578</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. YURTSEVEN</t>
+          <t>G. GRINVALDS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.539</v>
+        <v>-0.2812</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.1747</v>
+        <v>-0.7016</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6355999999999999</v>
+        <v>0.4204</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0005</v>
+        <v>-0.4738</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0058</v>
+        <v>0.1579</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.005200000000000093</v>
+        <v>-0.6317</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1904</v>
+        <v>-0.7896</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3712</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8192</v>
+        <v>-0.7896</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1899</v>
+        <v>0.3159</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3654</v>
+        <v>0.1579</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8244999999999999</v>
+        <v>0.1579</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.9592</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.9184</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9593</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4226</v>
+        <v>0.0349</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6044</v>
+        <v>-0.0697</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1818</v>
+        <v>0.1046</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1577999999999999</v>
+        <v>0.1578</v>
       </c>
       <c r="W18" t="n">
         <v>0.1578</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3155999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>O. YURTSEVEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.3902</v>
+        <v>-2.4672</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4225</v>
+        <v>-3.105</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.9677</v>
+        <v>0.6378</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.5417</v>
+        <v>1.0005</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.3578</v>
+        <v>1.0058</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1839</v>
+        <v>-0.005200000000000093</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4011</v>
+        <v>3.1904</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6043000000000001</v>
+        <v>2.3712</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0054</v>
+        <v>0.8192</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.9427</v>
+        <v>-2.1899</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7535</v>
+        <v>-1.3654</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.1893</v>
+        <v>-0.8244999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5934</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.552700000000001</v>
+        <v>-5.9184</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9592</v>
+        <v>2.9593</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2213</v>
+        <v>-0.3507</v>
       </c>
       <c r="T19" t="n">
-        <v>3.4135</v>
+        <v>-0.5347</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1922</v>
+        <v>0.1840000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4764</v>
+        <v>-0.1577999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3156</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.792</v>
+        <v>-0.3155999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>-8.4095</v>
+        <v>-6.0555</v>
       </c>
       <c r="E20" t="n">
-        <v>-12.1328</v>
+        <v>-2.5545</v>
       </c>
       <c r="F20" t="n">
-        <v>3.7231</v>
+        <v>-3.500999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-17.5203</v>
+        <v>-3.5417</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.8449</v>
+        <v>-2.3578</v>
       </c>
       <c r="I20" t="n">
-        <v>-14.6758</v>
+        <v>-1.1839</v>
       </c>
       <c r="J20" t="n">
-        <v>1.887900000000001</v>
+        <v>0.4011</v>
       </c>
       <c r="K20" t="n">
-        <v>6.6554</v>
+        <v>-0.6043000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>-4.7679</v>
+        <v>1.0054</v>
       </c>
       <c r="M20" t="n">
-        <v>-19.4087</v>
+        <v>-3.9427</v>
       </c>
       <c r="N20" t="n">
-        <v>-9.5</v>
+        <v>-1.7535</v>
       </c>
       <c r="O20" t="n">
-        <v>-9.908100000000001</v>
+        <v>-2.1893</v>
       </c>
       <c r="P20" t="n">
-        <v>15.9343</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q20" t="n">
-        <v>-23.2188</v>
+        <v>-4.552700000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>39.1529</v>
+        <v>2.9592</v>
       </c>
       <c r="S20" t="n">
-        <v>-21.9727</v>
+        <v>0.5560999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-14.9429</v>
+        <v>1.2814</v>
       </c>
       <c r="U20" t="n">
-        <v>-7.029500000000001</v>
+        <v>-0.7254999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>15.1496</v>
+        <v>-1.4764</v>
       </c>
       <c r="W20" t="n">
-        <v>24.1409</v>
+        <v>0.3156</v>
       </c>
       <c r="X20" t="n">
-        <v>-8.991399999999999</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>33</v>
       </c>
       <c r="D21" t="n">
-        <v>243.1562</v>
+        <v>271.5183</v>
       </c>
       <c r="E21" t="n">
-        <v>200.5307</v>
+        <v>209.9412</v>
       </c>
       <c r="F21" t="n">
-        <v>42.62489999999999</v>
+        <v>61.5777</v>
       </c>
       <c r="G21" t="n">
         <v>133.0708</v>
@@ -2062,13 +2062,13 @@
         <v>124.4934</v>
       </c>
       <c r="I21" t="n">
-        <v>8.578299999999999</v>
+        <v>8.578299999999993</v>
       </c>
       <c r="J21" t="n">
         <v>374.7476</v>
       </c>
       <c r="K21" t="n">
-        <v>254.4299999999999</v>
+        <v>254.43</v>
       </c>
       <c r="L21" t="n">
         <v>120.3156</v>
@@ -2083,25 +2083,25 @@
         <v>-111.7377</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.274899999999999</v>
+        <v>-2.274900000000008</v>
       </c>
       <c r="Q21" t="n">
-        <v>-491.6857</v>
+        <v>-491.6857000000001</v>
       </c>
       <c r="R21" t="n">
-        <v>489.4105999999999</v>
+        <v>489.4106</v>
       </c>
       <c r="S21" t="n">
-        <v>30.2498</v>
+        <v>58.6117</v>
       </c>
       <c r="T21" t="n">
-        <v>11.5004</v>
+        <v>20.9083</v>
       </c>
       <c r="U21" t="n">
-        <v>18.7519</v>
+        <v>37.7033</v>
       </c>
       <c r="V21" t="n">
-        <v>82.11190000000002</v>
+        <v>82.11190000000001</v>
       </c>
       <c r="W21" t="n">
         <v>305.9695</v>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Real Madrid.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Real Madrid.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D21" t="n">
         <v>271.5183</v>
